--- a/strategy_packs/garp_estrategia.xlsx
+++ b/strategy_packs/garp_estrategia.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -433,6 +433,11 @@
           <t>filter_conditions</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publica</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -448,6 +453,11 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>{"op": "AND", "children": [{"cond": {"left": {"type": "indicator", "key": "fundamental_pe_ttm"}, "operator": "&gt;", "right": {"type": "const", "value": 0}}}, {"cond": {"left": {"type": "indicator", "key": "fundamental_pe_ttm"}, "operator": "&lt;", "right": {"type": "const", "value": 60}}}, {"cond": {"left": {"type": "indicator", "key": "dist_sma200"}, "operator": "&gt;", "right": {"type": "const", "value": -10}}}, {"cond": {"left": {"type": "indicator", "key": "volatility_daily"}, "operator": "not_in", "right": {"type": "const", "value": ["extrema_corta", "extrema_media", "extrema_larga"]}}}]}</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -511,9 +521,6 @@
       <c r="C2" t="n">
         <v>3</v>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -529,9 +536,6 @@
       <c r="C3" t="n">
         <v>3</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -547,9 +551,6 @@
       <c r="C4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -565,9 +566,6 @@
       <c r="C5" t="n">
         <v>1</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/strategy_packs/garp_estrategia.xlsx
+++ b/strategy_packs/garp_estrategia.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,21 +491,6 @@
           <t>weight</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>scope</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>group_type</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>group_id</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
